--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:11</t>
+    <t xml:space="preserve">2026-09-24 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -831,19 +831,19 @@
         <v>22</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>-0.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -854,19 +854,19 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-0.18</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16">
@@ -877,19 +877,19 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -900,19 +900,19 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:02</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -515,7 +515,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_median_a_2020_coquimbo.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
